--- a/output/roomself_excel/8676.xlsx
+++ b/output/roomself_excel/8676.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>192205</v>
+        <v>184213</v>
       </c>
       <c r="D2" t="n">
-        <v>3572</v>
+        <v>3544</v>
       </c>
       <c r="E2" t="n">
-        <v>513</v>
+        <v>433</v>
       </c>
       <c r="F2" t="n">
-        <v>437</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>967493</v>
+        <v>12948</v>
       </c>
       <c r="D3" t="n">
-        <v>15596</v>
+        <v>976</v>
       </c>
       <c r="E3" t="n">
-        <v>1464</v>
+        <v>195</v>
       </c>
       <c r="F3" t="n">
-        <v>965</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4">
@@ -510,17 +510,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>120901</v>
+        <v>23310</v>
       </c>
       <c r="D4" t="n">
-        <v>2792</v>
+        <v>1364</v>
       </c>
       <c r="E4" t="n">
-        <v>319</v>
+        <v>179</v>
       </c>
       <c r="F4" t="n">
         <v>29</v>
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38982</v>
+        <v>192205</v>
       </c>
       <c r="D5" t="n">
-        <v>1588</v>
+        <v>3572</v>
       </c>
       <c r="E5" t="n">
-        <v>178</v>
+        <v>513</v>
       </c>
       <c r="F5" t="n">
-        <v>29</v>
+        <v>437</v>
       </c>
     </row>
     <row r="6">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>115710</v>
+        <v>783280</v>
       </c>
       <c r="D6" t="n">
-        <v>2764</v>
+        <v>12464</v>
       </c>
       <c r="E6" t="n">
-        <v>435</v>
+        <v>1464</v>
       </c>
       <c r="F6" t="n">
-        <v>314</v>
+        <v>965</v>
       </c>
     </row>
     <row r="7">
@@ -580,16 +580,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>202182</v>
+        <v>120901</v>
       </c>
       <c r="D7" t="n">
-        <v>4604</v>
+        <v>2792</v>
       </c>
       <c r="E7" t="n">
-        <v>530</v>
+        <v>319</v>
       </c>
       <c r="F7" t="n">
-        <v>505</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -602,13 +602,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>56970</v>
+        <v>38982</v>
       </c>
       <c r="D8" t="n">
-        <v>1924</v>
+        <v>1588</v>
       </c>
       <c r="E8" t="n">
-        <v>270</v>
+        <v>178</v>
       </c>
       <c r="F8" t="n">
         <v>29</v>
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>76142</v>
+        <v>115710</v>
       </c>
       <c r="D9" t="n">
-        <v>3096</v>
+        <v>2764</v>
       </c>
       <c r="E9" t="n">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="F9" t="n">
-        <v>393</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>47004</v>
+        <v>202182</v>
       </c>
       <c r="D10" t="n">
-        <v>2096</v>
+        <v>4604</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>505</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -668,13 +668,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>125712</v>
+        <v>56970</v>
       </c>
       <c r="D11" t="n">
-        <v>2848</v>
+        <v>1924</v>
       </c>
       <c r="E11" t="n">
-        <v>324</v>
+        <v>270</v>
       </c>
       <c r="F11" t="n">
         <v>29</v>
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12948</v>
+        <v>76142</v>
       </c>
       <c r="D12" t="n">
-        <v>976</v>
+        <v>3096</v>
       </c>
       <c r="E12" t="n">
-        <v>195</v>
+        <v>439</v>
       </c>
       <c r="F12" t="n">
-        <v>106</v>
+        <v>393</v>
       </c>
     </row>
     <row r="13">
@@ -712,16 +712,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26730</v>
+        <v>47004</v>
       </c>
       <c r="D13" t="n">
-        <v>1308</v>
+        <v>2096</v>
       </c>
       <c r="E13" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -730,19 +730,41 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23310</v>
+        <v>125712</v>
       </c>
       <c r="D14" t="n">
-        <v>1364</v>
+        <v>2848</v>
       </c>
       <c r="E14" t="n">
-        <v>179</v>
+        <v>324</v>
       </c>
       <c r="F14" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>26730</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1308</v>
+      </c>
+      <c r="E15" t="n">
+        <v>165</v>
+      </c>
+      <c r="F15" t="n">
         <v>29</v>
       </c>
     </row>

--- a/output/roomself_excel/8676.xlsx
+++ b/output/roomself_excel/8676.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>3544</v>
       </c>
-      <c r="E2" t="n">
-        <v>433</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>125</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +525,27 @@
       <c r="D3" t="n">
         <v>976</v>
       </c>
-      <c r="E3" t="n">
-        <v>195</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>106</v>
+        <v>166</v>
+      </c>
+      <c r="G3" t="n">
+        <v>28</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>78</v>
+      </c>
+      <c r="J3" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -519,12 +563,20 @@
       <c r="D4" t="n">
         <v>1364</v>
       </c>
-      <c r="E4" t="n">
-        <v>179</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>29</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="G4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,11 +593,27 @@
       <c r="D5" t="n">
         <v>3572</v>
       </c>
-      <c r="E5" t="n">
-        <v>513</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>437</v>
+        <v>409</v>
+      </c>
+      <c r="G5" t="n">
+        <v>29</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>483</v>
+      </c>
+      <c r="J5" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +631,20 @@
       <c r="D6" t="n">
         <v>12464</v>
       </c>
-      <c r="E6" t="n">
-        <v>1464</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>965</v>
-      </c>
+        <v>1383</v>
+      </c>
+      <c r="G6" t="n">
+        <v>29</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +661,20 @@
       <c r="D7" t="n">
         <v>2792</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>319</v>
       </c>
-      <c r="F7" t="n">
-        <v>29</v>
-      </c>
+      <c r="G7" t="n">
+        <v>29</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +691,20 @@
       <c r="D8" t="n">
         <v>1588</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>178</v>
       </c>
-      <c r="F8" t="n">
-        <v>29</v>
-      </c>
+      <c r="G8" t="n">
+        <v>29</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,11 +721,27 @@
       <c r="D9" t="n">
         <v>2764</v>
       </c>
-      <c r="E9" t="n">
-        <v>435</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>314</v>
+        <v>285</v>
+      </c>
+      <c r="G9" t="n">
+        <v>29</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>406</v>
+      </c>
+      <c r="J9" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="10">
@@ -651,11 +759,27 @@
       <c r="D10" t="n">
         <v>4604</v>
       </c>
-      <c r="E10" t="n">
-        <v>505</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>234</v>
+        <v>205</v>
+      </c>
+      <c r="G10" t="n">
+        <v>29</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>476</v>
+      </c>
+      <c r="J10" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="11">
@@ -673,12 +797,20 @@
       <c r="D11" t="n">
         <v>1924</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>270</v>
       </c>
-      <c r="F11" t="n">
-        <v>29</v>
-      </c>
+      <c r="G11" t="n">
+        <v>29</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,11 +827,27 @@
       <c r="D12" t="n">
         <v>3096</v>
       </c>
-      <c r="E12" t="n">
-        <v>439</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>393</v>
+        <v>231</v>
+      </c>
+      <c r="G12" t="n">
+        <v>28</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>273</v>
+      </c>
+      <c r="J12" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="13">
@@ -717,12 +865,12 @@
       <c r="D13" t="n">
         <v>2096</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +887,20 @@
       <c r="D14" t="n">
         <v>2848</v>
       </c>
-      <c r="E14" t="n">
-        <v>324</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>29</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="G14" t="n">
+        <v>29</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +917,20 @@
       <c r="D15" t="n">
         <v>1308</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>165</v>
       </c>
-      <c r="F15" t="n">
-        <v>29</v>
-      </c>
+      <c r="G15" t="n">
+        <v>29</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
